--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988297</v>
       </c>
       <c r="B2" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136988463</v>
       </c>
       <c r="B3" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136989351</v>
       </c>
       <c r="B4" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136989393</v>
       </c>
       <c r="B5" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104073</v>
+        <v>104079</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988297</v>
       </c>
       <c r="B2" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136988463</v>
       </c>
       <c r="B3" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136989351</v>
       </c>
       <c r="B4" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136989393</v>
       </c>
       <c r="B5" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104079</v>
+        <v>104081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988297</v>
       </c>
       <c r="B2" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136988463</v>
       </c>
       <c r="B3" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136989351</v>
       </c>
       <c r="B4" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136989393</v>
       </c>
       <c r="B5" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104081</v>
+        <v>104082</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988297</v>
       </c>
       <c r="B2" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136988463</v>
       </c>
       <c r="B3" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136989351</v>
       </c>
       <c r="B4" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136989393</v>
       </c>
       <c r="B5" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104082</v>
+        <v>104088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988297</v>
       </c>
       <c r="B2" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136988463</v>
       </c>
       <c r="B3" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136989351</v>
       </c>
       <c r="B4" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136989393</v>
       </c>
       <c r="B5" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104088</v>
+        <v>104092</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988297</v>
       </c>
       <c r="B2" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136988463</v>
       </c>
       <c r="B3" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136989351</v>
       </c>
       <c r="B4" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136989393</v>
       </c>
       <c r="B5" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104092</v>
+        <v>104094</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988297</v>
       </c>
       <c r="B2" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136988463</v>
       </c>
       <c r="B3" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136989351</v>
       </c>
       <c r="B4" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136989393</v>
       </c>
       <c r="B5" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104094</v>
+        <v>104096</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988297</v>
       </c>
       <c r="B2" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136988463</v>
       </c>
       <c r="B3" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136989351</v>
       </c>
       <c r="B4" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136989393</v>
       </c>
       <c r="B5" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104096</v>
+        <v>104109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988297</v>
       </c>
       <c r="B2" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136988463</v>
       </c>
       <c r="B3" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136989351</v>
       </c>
       <c r="B4" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136989393</v>
       </c>
       <c r="B5" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104109</v>
+        <v>104111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988297</v>
       </c>
       <c r="B2" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136988463</v>
       </c>
       <c r="B3" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136989351</v>
       </c>
       <c r="B4" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136989393</v>
       </c>
       <c r="B5" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104111</v>
+        <v>104114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988297</v>
       </c>
       <c r="B2" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136988463</v>
       </c>
       <c r="B3" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136989351</v>
       </c>
       <c r="B4" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136989393</v>
       </c>
       <c r="B5" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104114</v>
+        <v>104129</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988297</v>
       </c>
       <c r="B2" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136988463</v>
       </c>
       <c r="B3" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136989351</v>
       </c>
       <c r="B4" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136989393</v>
       </c>
       <c r="B5" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104129</v>
+        <v>104130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988297</v>
       </c>
       <c r="B2" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136988463</v>
       </c>
       <c r="B3" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136989351</v>
       </c>
       <c r="B4" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136989393</v>
       </c>
       <c r="B5" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104130</v>
+        <v>104135</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988297</v>
       </c>
       <c r="B2" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136988463</v>
       </c>
       <c r="B3" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136989351</v>
       </c>
       <c r="B4" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136989393</v>
       </c>
       <c r="B5" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104135</v>
+        <v>104138</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988297</v>
       </c>
       <c r="B2" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136988463</v>
       </c>
       <c r="B3" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136989351</v>
       </c>
       <c r="B4" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136989393</v>
       </c>
       <c r="B5" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104138</v>
+        <v>104144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104144</v>
+        <v>104145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988297</v>
       </c>
       <c r="B2" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136988463</v>
       </c>
       <c r="B3" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136989351</v>
       </c>
       <c r="B4" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136989393</v>
       </c>
       <c r="B5" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104145</v>
+        <v>104157</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988297</v>
       </c>
       <c r="B2" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136988463</v>
       </c>
       <c r="B3" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136989351</v>
       </c>
       <c r="B4" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136989393</v>
       </c>
       <c r="B5" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104157</v>
+        <v>104158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988297</v>
       </c>
       <c r="B2" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136988463</v>
       </c>
       <c r="B3" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136989351</v>
       </c>
       <c r="B4" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136989393</v>
       </c>
       <c r="B5" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104158</v>
+        <v>104161</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988297</v>
       </c>
       <c r="B2" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136988463</v>
       </c>
       <c r="B3" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136989351</v>
       </c>
       <c r="B4" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136989393</v>
       </c>
       <c r="B5" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104161</v>
+        <v>104162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2026 artfynd.xlsx
+++ b/artfynd/A 35099-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988297</v>
       </c>
       <c r="B2" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136988463</v>
       </c>
       <c r="B3" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136989351</v>
       </c>
       <c r="B4" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136989393</v>
       </c>
       <c r="B5" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136989462</v>
       </c>
       <c r="B6" t="n">
-        <v>104162</v>
+        <v>104166</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
